--- a/course-design-2/outputs/tables/ch4/41_stage26_2_fact_verification.xlsx
+++ b/course-design-2/outputs/tables/ch4/41_stage26_2_fact_verification.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_三种划分样本量" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_T2口径与gap实测" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_T2日历天分布" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_阈值敏感性_统一口径" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_口径对比与变化" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_SafeF退化与精简" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_消融结果（精简SafeF）" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_消融跨度与维度" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="01_三种划分样本量" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_T2统计范围与gap实测" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_T2日历天分布" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_阈值敏感性_统一统计范围" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="05_统计范围对比与变化" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="06_SafeF退化与精简" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="07_消融结果（精简SafeF）" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="08_消融跨度与维度" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,7 +964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>统计范围</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1221,7 +1221,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Stage26.2 统一口径</t>
+          <t>Stage26.2 统一统计范围</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1579,7 +1579,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>严格口径多周期岗位数（代表周期口径）</t>
+          <t>严格统计范围多周期岗位数（代表周期统计范围）</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1611,7 +1611,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>正文口径要求</t>
+          <t>正文范围要求</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1795,22 +1795,22 @@
         <v>258</v>
       </c>
       <c r="D4" t="n">
-        <v>36.404508</v>
+        <v>36.647554</v>
       </c>
       <c r="E4" t="n">
-        <v>71.194016</v>
+        <v>70.343412</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5739880000000001</v>
+        <v>0.584107</v>
       </c>
       <c r="G4" t="n">
-        <v>36.503104</v>
+        <v>36.163977</v>
       </c>
       <c r="H4" t="n">
-        <v>66.75133599999999</v>
+        <v>66.475624</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5568</v>
+        <v>0.560454</v>
       </c>
       <c r="J4" t="n">
         <v>10418</v>
@@ -1837,22 +1837,22 @@
         <v>320</v>
       </c>
       <c r="D5" t="n">
-        <v>36.088217</v>
+        <v>36.206167</v>
       </c>
       <c r="E5" t="n">
-        <v>69.294882</v>
+        <v>69.574967</v>
       </c>
       <c r="F5" t="n">
-        <v>0.596413</v>
+        <v>0.593144</v>
       </c>
       <c r="G5" t="n">
-        <v>36.074723</v>
+        <v>36.099666</v>
       </c>
       <c r="H5" t="n">
-        <v>66.307726</v>
+        <v>66.191014</v>
       </c>
       <c r="I5" t="n">
-        <v>0.562671</v>
+        <v>0.564209</v>
       </c>
       <c r="J5" t="n">
         <v>10418</v>
@@ -1879,22 +1879,22 @@
         <v>322</v>
       </c>
       <c r="D6" t="n">
-        <v>36.244749</v>
+        <v>36.223222</v>
       </c>
       <c r="E6" t="n">
-        <v>69.80971599999999</v>
+        <v>69.97754500000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.590394</v>
+        <v>0.588422</v>
       </c>
       <c r="G6" t="n">
-        <v>36.182513</v>
+        <v>36.300561</v>
       </c>
       <c r="H6" t="n">
-        <v>66.278603</v>
+        <v>66.542643</v>
       </c>
       <c r="I6" t="n">
-        <v>0.563055</v>
+        <v>0.559567</v>
       </c>
       <c r="J6" t="n">
         <v>10418</v>
@@ -1990,11 +1990,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A+B+C+E</t>
+          <t>A+B+C+D+E+SafeF</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.503104</v>
+        <v>36.300561</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.710326999999999</v>
+        <v>1.507784000000001</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5114429999999999</v>
+        <v>0.4516559999999998</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -2112,13 +2112,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36.088217</v>
+        <v>36.206167</v>
       </c>
       <c r="F9" t="n">
-        <v>36.244749</v>
+        <v>36.223222</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1565319999999986</v>
+        <v>-0.01705499999999915</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2136,13 +2136,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>36.074723</v>
+        <v>36.099666</v>
       </c>
       <c r="F10" t="n">
-        <v>36.182513</v>
+        <v>36.300561</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1077900000000014</v>
+        <v>-0.2008950000000027</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>

--- a/course-design-2/outputs/tables/ch4/41_stage26_2_fact_verification.xlsx
+++ b/course-design-2/outputs/tables/ch4/41_stage26_2_fact_verification.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_三种划分样本量" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_T2统计范围与gap实测" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_T2日历天分布" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_阈值敏感性_统一统计范围" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="05_统计范围对比与变化" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06_SafeF退化与精简" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="07_消融结果（精简SafeF）" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="08_消融跨度与维度" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_三种划分样本量" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_T2统计范围与gap实测" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_T2日历天分布" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_阈值敏感性_统一统计范围" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_统计范围对比与变化" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_SafeF退化与精简" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_消融结果（精简SafeF）" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_消融跨度与维度" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1221,7 +1221,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Stage26.2 统一统计范围</t>
+          <t>Stage26.2 统一口径</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1351,8 +1351,6 @@
       <c r="F2" t="n">
         <v>0.56211785</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1377,8 +1375,6 @@
       <c r="F3" t="n">
         <v>0.22152792</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1403,8 +1399,6 @@
       <c r="F4" t="n">
         <v>0.99986562</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1429,8 +1423,6 @@
       <c r="F5" t="n">
         <v>0.99986562</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1455,8 +1447,6 @@
       <c r="F6" t="n">
         <v>0.99986562</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1481,16 +1471,8 @@
       <c r="F7" t="n">
         <v>0.5</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Stage26.1 Safe-F 特征数</t>
@@ -1501,12 +1483,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Stage26.2 精简后 Safe-F 特征数</t>
@@ -1517,12 +1493,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>精简后特征清单</t>
@@ -1535,12 +1505,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>被移出预测模型的特征</t>
@@ -1553,12 +1517,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>被移出特征的去向</t>
@@ -1571,15 +1529,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>严格统计范围多周期岗位数（代表周期统计范围）</t>
+          <t>严格口径多周期岗位数（代表周期口径）</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1587,12 +1539,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>previous_reopen_gap_days 缺失数</t>
@@ -1603,15 +1549,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>正文范围要求</t>
+          <t>正文口径要求</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1795,22 +1735,22 @@
         <v>258</v>
       </c>
       <c r="D4" t="n">
-        <v>36.647554</v>
+        <v>36.404508</v>
       </c>
       <c r="E4" t="n">
-        <v>70.343412</v>
+        <v>71.194016</v>
       </c>
       <c r="F4" t="n">
-        <v>0.584107</v>
+        <v>0.5739880000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>36.163977</v>
+        <v>36.503104</v>
       </c>
       <c r="H4" t="n">
-        <v>66.475624</v>
+        <v>66.75133599999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.560454</v>
+        <v>0.5568</v>
       </c>
       <c r="J4" t="n">
         <v>10418</v>
@@ -1837,22 +1777,22 @@
         <v>320</v>
       </c>
       <c r="D5" t="n">
-        <v>36.206167</v>
+        <v>36.088217</v>
       </c>
       <c r="E5" t="n">
-        <v>69.574967</v>
+        <v>69.294882</v>
       </c>
       <c r="F5" t="n">
-        <v>0.593144</v>
+        <v>0.596413</v>
       </c>
       <c r="G5" t="n">
-        <v>36.099666</v>
+        <v>36.074723</v>
       </c>
       <c r="H5" t="n">
-        <v>66.191014</v>
+        <v>66.307726</v>
       </c>
       <c r="I5" t="n">
-        <v>0.564209</v>
+        <v>0.562671</v>
       </c>
       <c r="J5" t="n">
         <v>10418</v>
@@ -1879,22 +1819,22 @@
         <v>322</v>
       </c>
       <c r="D6" t="n">
-        <v>36.223222</v>
+        <v>36.244749</v>
       </c>
       <c r="E6" t="n">
-        <v>69.97754500000001</v>
+        <v>69.80971599999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.588422</v>
+        <v>0.590394</v>
       </c>
       <c r="G6" t="n">
-        <v>36.300561</v>
+        <v>36.182513</v>
       </c>
       <c r="H6" t="n">
-        <v>66.542643</v>
+        <v>66.278603</v>
       </c>
       <c r="I6" t="n">
-        <v>0.559567</v>
+        <v>0.563055</v>
       </c>
       <c r="J6" t="n">
         <v>10418</v>
@@ -1976,11 +1916,6 @@
       <c r="C2" t="n">
         <v>34.792777</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1990,17 +1925,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A+B+C+D+E+SafeF</t>
+          <t>A+B+C+E</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.300561</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+        <v>36.503104</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2014,13 +1944,8 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.507784000000001</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+        <v>1.710326999999999</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2034,13 +1959,8 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.4516559999999998</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+        <v>0.5114429999999999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2056,11 +1976,6 @@
       <c r="C6" t="n">
         <v>320</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2076,11 +1991,6 @@
       <c r="C7" t="n">
         <v>322</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2096,29 +2006,21 @@
       <c r="C8" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>validation</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36.206167</v>
+        <v>36.088217</v>
       </c>
       <c r="F9" t="n">
-        <v>36.223222</v>
+        <v>36.244749</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.01705499999999915</v>
+        <v>-0.1565319999999986</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2127,22 +2029,19 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>36.099666</v>
+        <v>36.074723</v>
       </c>
       <c r="F10" t="n">
-        <v>36.300561</v>
+        <v>36.182513</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2008950000000027</v>
+        <v>-0.1077900000000014</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
